--- a/week-01/Lee_Idasha_DataCleaning.xlsx
+++ b/week-01/Lee_Idasha_DataCleaning.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -21,12 +21,15 @@
     <sheet name="Clean Data" sheetId="2" r:id="rId6"/>
     <sheet name="Clean Log" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId8"/>
-    <pivotCache cacheId="14" r:id="rId9"/>
+    <pivotCache cacheId="348" r:id="rId8"/>
+    <pivotCache cacheId="349" r:id="rId9"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -742,6 +745,51 @@
     <t xml:space="preserve"> customer100@company.com </t>
   </si>
   <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of TotalSales</t>
+  </si>
+  <si>
+    <t>Count of OrderID</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Elizabeth Davis</t>
+  </si>
+  <si>
+    <t>Elizabeth Johnson</t>
+  </si>
+  <si>
+    <t>Elizabeth Taylor</t>
+  </si>
+  <si>
+    <t>James Moore</t>
+  </si>
+  <si>
+    <t>Linda Davis</t>
+  </si>
+  <si>
+    <t>Linda Moore</t>
+  </si>
+  <si>
+    <t>Linda Thomas</t>
+  </si>
+  <si>
+    <t>Michael Thomas</t>
+  </si>
+  <si>
+    <t>Robert Anderson</t>
+  </si>
+  <si>
+    <t>Robert Wilson</t>
+  </si>
+  <si>
+    <t>Details for Sum of TotalSales - CleanProduct: Laptop</t>
+  </si>
+  <si>
     <t xml:space="preserve">NameClean
 </t>
   </si>
@@ -771,6 +819,438 @@
     <t>LastName</t>
   </si>
   <si>
+    <t>patricia wilson</t>
+  </si>
+  <si>
+    <t>Patricia Wilson</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>robert wilson</t>
+  </si>
+  <si>
+    <t>San Antonio, TX</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>MICHAEL THOMAS</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>James DAVIS</t>
+  </si>
+  <si>
+    <t>James Davis</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>LINDA moore</t>
+  </si>
+  <si>
+    <t>Moore</t>
+  </si>
+  <si>
+    <t>Barbara Wilson</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>Barbara</t>
+  </si>
+  <si>
+    <t>ELIZABETH moore</t>
+  </si>
+  <si>
+    <t>Elizabeth Moore</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>william THOMAS</t>
+  </si>
+  <si>
+    <t>William Thomas</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>ELIZABETH JOHNSON</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>ELIZABETH TAYLOR</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>ELIZABETH jackson</t>
+  </si>
+  <si>
+    <t>Elizabeth Jackson</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>william wilson</t>
+  </si>
+  <si>
+    <t>William Wilson</t>
+  </si>
+  <si>
+    <t>ELIZABETH DAVIS</t>
+  </si>
+  <si>
+    <t>john jackson</t>
+  </si>
+  <si>
+    <t>John Jackson</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>LINDA DAVIS</t>
+  </si>
+  <si>
+    <t>robert Anderson</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>James moore</t>
+  </si>
+  <si>
+    <t>Barbara Thomas</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>patricia TAYLOR</t>
+  </si>
+  <si>
+    <t>Patricia Taylor</t>
+  </si>
+  <si>
+    <t>MICHAEL jackson</t>
+  </si>
+  <si>
+    <t>Michael Jackson</t>
+  </si>
+  <si>
+    <t>robert JOHNSON</t>
+  </si>
+  <si>
+    <t>Robert Johnson</t>
+  </si>
+  <si>
+    <t>MARY wilson</t>
+  </si>
+  <si>
+    <t>Mary Wilson</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>MICHAEL TAYLOR</t>
+  </si>
+  <si>
+    <t>Michael Taylor</t>
+  </si>
+  <si>
+    <t>robert DAVIS</t>
+  </si>
+  <si>
+    <t>Robert Davis</t>
+  </si>
+  <si>
+    <t>ELIZABETH brown</t>
+  </si>
+  <si>
+    <t>Elizabeth Brown</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>barbara DAVIS</t>
+  </si>
+  <si>
+    <t>Barbara Davis</t>
+  </si>
+  <si>
+    <t>patricia JOHNSON</t>
+  </si>
+  <si>
+    <t>Patricia Johnson</t>
+  </si>
+  <si>
+    <t>ELIZABETH wilson</t>
+  </si>
+  <si>
+    <t>Elizabeth Wilson</t>
+  </si>
+  <si>
+    <t>robert TAYLOR</t>
+  </si>
+  <si>
+    <t>Robert Taylor</t>
+  </si>
+  <si>
+    <t>MICHAEL moore</t>
+  </si>
+  <si>
+    <t>Michael Moore</t>
+  </si>
+  <si>
+    <t>patricia moore</t>
+  </si>
+  <si>
+    <t>Patricia Moore</t>
+  </si>
+  <si>
+    <t>LINDA Anderson</t>
+  </si>
+  <si>
+    <t>Linda Anderson</t>
+  </si>
+  <si>
+    <t>william Anderson</t>
+  </si>
+  <si>
+    <t>William Anderson</t>
+  </si>
+  <si>
+    <t>MARY DAVIS</t>
+  </si>
+  <si>
+    <t>Mary Davis</t>
+  </si>
+  <si>
+    <t>patricia jackson</t>
+  </si>
+  <si>
+    <t>Patricia Jackson</t>
+  </si>
+  <si>
+    <t>Barbara Taylor</t>
+  </si>
+  <si>
+    <t>James jackson</t>
+  </si>
+  <si>
+    <t>James Jackson</t>
+  </si>
+  <si>
+    <t>Barbara Johnson</t>
+  </si>
+  <si>
+    <t>william TAYLOR</t>
+  </si>
+  <si>
+    <t>William Taylor</t>
+  </si>
+  <si>
+    <t>MARY moore</t>
+  </si>
+  <si>
+    <t>Mary Moore</t>
+  </si>
+  <si>
+    <t>Linda Wilson</t>
+  </si>
+  <si>
+    <t>MICHAEL Anderson</t>
+  </si>
+  <si>
+    <t>Michael Anderson</t>
+  </si>
+  <si>
+    <t>MARY TAYLOR</t>
+  </si>
+  <si>
+    <t>Mary Taylor</t>
+  </si>
+  <si>
+    <t>ELIZABETH THOMAS</t>
+  </si>
+  <si>
+    <t>Elizabeth Thomas</t>
+  </si>
+  <si>
+    <t>barbara smith</t>
+  </si>
+  <si>
+    <t>Barbara Smith</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>robert brown</t>
+  </si>
+  <si>
+    <t>Robert Brown</t>
+  </si>
+  <si>
+    <t>James wilson</t>
+  </si>
+  <si>
+    <t>James Wilson</t>
+  </si>
+  <si>
+    <t>john wilson</t>
+  </si>
+  <si>
+    <t>John Wilson</t>
+  </si>
+  <si>
+    <t>Linda Johnson</t>
+  </si>
+  <si>
+    <t>LINDA brown</t>
+  </si>
+  <si>
+    <t>Linda Brown</t>
+  </si>
+  <si>
+    <t>robert moore</t>
+  </si>
+  <si>
+    <t>Robert Moore</t>
+  </si>
+  <si>
+    <t>James smith</t>
+  </si>
+  <si>
+    <t>James Smith</t>
+  </si>
+  <si>
+    <t>john moore</t>
+  </si>
+  <si>
+    <t>John Moore</t>
+  </si>
+  <si>
+    <t>James Anderson</t>
+  </si>
+  <si>
+    <t>patricia THOMAS</t>
+  </si>
+  <si>
+    <t>Patricia Thomas</t>
+  </si>
+  <si>
+    <t>barbara brown</t>
+  </si>
+  <si>
+    <t>Barbara Brown</t>
+  </si>
+  <si>
+    <t>LINDA smith</t>
+  </si>
+  <si>
+    <t>Linda Smith</t>
+  </si>
+  <si>
+    <t>john DAVIS</t>
+  </si>
+  <si>
+    <t>John Davis</t>
+  </si>
+  <si>
+    <t>john Anderson</t>
+  </si>
+  <si>
+    <t>John Anderson</t>
+  </si>
+  <si>
+    <t>Linda Taylor</t>
+  </si>
+  <si>
+    <t>MARY smith</t>
+  </si>
+  <si>
+    <t>Mary Smith</t>
+  </si>
+  <si>
+    <t>john brown</t>
+  </si>
+  <si>
+    <t>John Brown</t>
+  </si>
+  <si>
+    <t>MARY THOMAS</t>
+  </si>
+  <si>
+    <t>Mary Thomas</t>
+  </si>
+  <si>
+    <t>william jackson</t>
+  </si>
+  <si>
+    <t>William Jackson</t>
+  </si>
+  <si>
     <t>Completed 
 Task</t>
   </si>
@@ -782,32 +1262,35 @@
 were affected?</t>
   </si>
   <si>
-    <t>Records were calculated</t>
-  </si>
-  <si>
     <t>Noticeable 
 Problems</t>
   </si>
   <si>
+    <t>Records were calculated</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
     <t>name format</t>
   </si>
   <si>
+    <t>OrderID Repears</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
     <t>duplicates</t>
   </si>
   <si>
-    <t>unit price not in currency</t>
-  </si>
-  <si>
-    <t>OrderID Repears</t>
-  </si>
-  <si>
     <t>Check if cells contain extra spacing</t>
   </si>
   <si>
-    <t>cells contain extra space</t>
-  </si>
-  <si>
-    <t>non printing charaters</t>
+    <t>A105,A106</t>
+  </si>
+  <si>
+    <t>no caps on states/ city, state</t>
   </si>
   <si>
     <t xml:space="preserve">Clean B2 </t>
@@ -816,13 +1299,20 @@
     <t>L2</t>
   </si>
   <si>
-    <t>A107,A108</t>
+    <t>symbols in products 
+($%#@!)</t>
   </si>
   <si>
     <t>Compare L2 with B2/ 
 Remove Hidden Charactes</t>
   </si>
   <si>
+    <t>A107,A108</t>
+  </si>
+  <si>
+    <t>unit price not in currency</t>
+  </si>
+  <si>
     <t>Compare B3 AND M3/ 
 TRIM</t>
   </si>
@@ -830,362 +1320,82 @@
     <t>A109,A10</t>
   </si>
   <si>
-    <t>A103</t>
-  </si>
-  <si>
-    <t>A104</t>
-  </si>
-  <si>
-    <t>A105,A106</t>
+    <t>cells contain extra space</t>
+  </si>
+  <si>
+    <t>Standardize the name</t>
   </si>
   <si>
     <t>N2</t>
   </si>
   <si>
-    <t>Standardize the name</t>
+    <t>non printing charaters</t>
+  </si>
+  <si>
+    <t>Filled name formula</t>
   </si>
   <si>
     <t>L2:N2</t>
   </si>
   <si>
-    <t>Filled name formula</t>
-  </si>
-  <si>
-    <t>symbols in products 
-($%#@!)</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
     <t>Remove Special Charaters from Product</t>
   </si>
   <si>
-    <t>Tablet</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>Keyboard</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
     <t>Column O</t>
   </si>
   <si>
+    <t>remove 30 @</t>
+  </si>
+  <si>
+    <t>Find &amp; Replace</t>
+  </si>
+  <si>
     <t>Column P</t>
   </si>
   <si>
-    <t>Find &amp; Replace</t>
-  </si>
-  <si>
-    <t>remove 30 @</t>
+    <t>remove 38 #</t>
+  </si>
+  <si>
+    <t>Exact returns equal TRUE</t>
+  </si>
+  <si>
+    <t>Column Q</t>
+  </si>
+  <si>
+    <t>remove 40 !</t>
+  </si>
+  <si>
+    <t>CountIF</t>
+  </si>
+  <si>
+    <t>A11</t>
   </si>
   <si>
     <t>remove 30 $</t>
   </si>
   <si>
-    <t>remove 38 #</t>
+    <t>Concate Column D and Column E</t>
+  </si>
+  <si>
+    <t>Column R</t>
   </si>
   <si>
     <t>remove 46 %</t>
   </si>
   <si>
-    <t>remove 40 !</t>
-  </si>
-  <si>
-    <t>Exact returns equal TRUE</t>
-  </si>
-  <si>
-    <t>Column Q</t>
-  </si>
-  <si>
-    <t>CountIF</t>
-  </si>
-  <si>
-    <t>A11</t>
-  </si>
-  <si>
-    <t>no caps on states/ city, state</t>
-  </si>
-  <si>
-    <t>Concate Column D and Column E</t>
-  </si>
-  <si>
-    <t>Column R</t>
-  </si>
-  <si>
-    <t>Patricia Taylor</t>
-  </si>
-  <si>
-    <t>Robert Wilson</t>
-  </si>
-  <si>
-    <t>Michael Jackson</t>
-  </si>
-  <si>
-    <t>Michael Thomas</t>
-  </si>
-  <si>
-    <t>Robert Johnson</t>
-  </si>
-  <si>
-    <t>Mary Wilson</t>
-  </si>
-  <si>
-    <t>Michael Taylor</t>
-  </si>
-  <si>
-    <t>Robert Davis</t>
-  </si>
-  <si>
-    <t>Elizabeth Brown</t>
-  </si>
-  <si>
-    <t>Elizabeth Johnson</t>
-  </si>
-  <si>
-    <t>Elizabeth Moore</t>
-  </si>
-  <si>
-    <t>Barbara Davis</t>
-  </si>
-  <si>
-    <t>Barbara Thomas</t>
-  </si>
-  <si>
-    <t>Patricia Johnson</t>
-  </si>
-  <si>
-    <t>Elizabeth Wilson</t>
-  </si>
-  <si>
-    <t>Robert Taylor</t>
-  </si>
-  <si>
-    <t>Michael Moore</t>
-  </si>
-  <si>
-    <t>Patricia Moore</t>
-  </si>
-  <si>
-    <t>Linda Anderson</t>
-  </si>
-  <si>
-    <t>William Anderson</t>
-  </si>
-  <si>
-    <t>Linda Moore</t>
-  </si>
-  <si>
-    <t>James Moore</t>
-  </si>
-  <si>
-    <t>Mary Davis</t>
-  </si>
-  <si>
-    <t>Patricia Jackson</t>
-  </si>
-  <si>
-    <t>Robert Anderson</t>
-  </si>
-  <si>
-    <t>Barbara Taylor</t>
-  </si>
-  <si>
-    <t>Linda Davis</t>
-  </si>
-  <si>
-    <t>James Jackson</t>
-  </si>
-  <si>
-    <t>Barbara Johnson</t>
-  </si>
-  <si>
-    <t>William Taylor</t>
-  </si>
-  <si>
-    <t>Mary Moore</t>
-  </si>
-  <si>
-    <t>John Jackson</t>
-  </si>
-  <si>
-    <t>Linda Wilson</t>
-  </si>
-  <si>
-    <t>Michael Anderson</t>
-  </si>
-  <si>
-    <t>Elizabeth Davis</t>
-  </si>
-  <si>
-    <t>Elizabeth Jackson</t>
-  </si>
-  <si>
-    <t>Mary Taylor</t>
-  </si>
-  <si>
-    <t>Elizabeth Thomas</t>
-  </si>
-  <si>
-    <t>Barbara Smith</t>
-  </si>
-  <si>
-    <t>Robert Brown</t>
-  </si>
-  <si>
-    <t>James Wilson</t>
-  </si>
-  <si>
-    <t>John Wilson</t>
-  </si>
-  <si>
-    <t>William Wilson</t>
-  </si>
-  <si>
-    <t>Patricia Wilson</t>
-  </si>
-  <si>
-    <t>Linda Johnson</t>
-  </si>
-  <si>
-    <t>Linda Brown</t>
-  </si>
-  <si>
-    <t>Robert Moore</t>
-  </si>
-  <si>
-    <t>James Smith</t>
-  </si>
-  <si>
-    <t>John Moore</t>
-  </si>
-  <si>
-    <t>James Anderson</t>
-  </si>
-  <si>
-    <t>Patricia Thomas</t>
-  </si>
-  <si>
-    <t>Barbara Brown</t>
-  </si>
-  <si>
-    <t>Linda Smith</t>
-  </si>
-  <si>
-    <t>John Davis</t>
-  </si>
-  <si>
-    <t>John Anderson</t>
-  </si>
-  <si>
-    <t>Elizabeth Taylor</t>
-  </si>
-  <si>
-    <t>Linda Taylor</t>
-  </si>
-  <si>
-    <t>Barbara Wilson</t>
-  </si>
-  <si>
-    <t>William Thomas</t>
-  </si>
-  <si>
-    <t>Mary Smith</t>
-  </si>
-  <si>
-    <t>John Brown</t>
-  </si>
-  <si>
-    <t>James Davis</t>
-  </si>
-  <si>
-    <t>Linda Thomas</t>
-  </si>
-  <si>
-    <t>Mary Thomas</t>
-  </si>
-  <si>
-    <t>William Jackson</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
-    <t>Taylor</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>Wilson</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Jackson</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>Moore</t>
-  </si>
-  <si>
-    <t>Barbara</t>
-  </si>
-  <si>
-    <t>Linda</t>
-  </si>
-  <si>
-    <t>Anderson</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
     <t>Seperated First and Last Name</t>
   </si>
   <si>
     <t>Column S and Column T</t>
+  </si>
+  <si>
+    <t>Duplicate OrderIDs (Highlight)</t>
   </si>
   <si>
     <t>A7&amp;A22(2006),
 A12&amp;A47 (2011)</t>
   </si>
   <si>
-    <t>Duplicate OrderIDs (Highlight)</t>
-  </si>
-  <si>
     <t>Remove Duplicates</t>
   </si>
   <si>
@@ -1205,198 +1415,6 @@
     <t>A12 - 56 High value Orders</t>
   </si>
   <si>
-    <t>patricia TAYLOR</t>
-  </si>
-  <si>
-    <t>Chicago, IL</t>
-  </si>
-  <si>
-    <t>robert wilson</t>
-  </si>
-  <si>
-    <t>San Antonio, TX</t>
-  </si>
-  <si>
-    <t>MICHAEL jackson</t>
-  </si>
-  <si>
-    <t>MICHAEL THOMAS</t>
-  </si>
-  <si>
-    <t>San Diego, CA</t>
-  </si>
-  <si>
-    <t>robert JOHNSON</t>
-  </si>
-  <si>
-    <t>Houston, TX</t>
-  </si>
-  <si>
-    <t>MARY wilson</t>
-  </si>
-  <si>
-    <t>MICHAEL TAYLOR</t>
-  </si>
-  <si>
-    <t>Los Angeles, CA</t>
-  </si>
-  <si>
-    <t>robert DAVIS</t>
-  </si>
-  <si>
-    <t>ELIZABETH brown</t>
-  </si>
-  <si>
-    <t>ELIZABETH JOHNSON</t>
-  </si>
-  <si>
-    <t>ELIZABETH moore</t>
-  </si>
-  <si>
-    <t>barbara DAVIS</t>
-  </si>
-  <si>
-    <t>Philadelphia, PA</t>
-  </si>
-  <si>
-    <t>patricia JOHNSON</t>
-  </si>
-  <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
-    <t>ELIZABETH wilson</t>
-  </si>
-  <si>
-    <t>Phoenix, AZ</t>
-  </si>
-  <si>
-    <t>robert TAYLOR</t>
-  </si>
-  <si>
-    <t>MICHAEL moore</t>
-  </si>
-  <si>
-    <t>patricia moore</t>
-  </si>
-  <si>
-    <t>LINDA Anderson</t>
-  </si>
-  <si>
-    <t>william Anderson</t>
-  </si>
-  <si>
-    <t>LINDA moore</t>
-  </si>
-  <si>
-    <t>James moore</t>
-  </si>
-  <si>
-    <t>MARY DAVIS</t>
-  </si>
-  <si>
-    <t>patricia jackson</t>
-  </si>
-  <si>
-    <t>robert Anderson</t>
-  </si>
-  <si>
-    <t>LINDA DAVIS</t>
-  </si>
-  <si>
-    <t>James jackson</t>
-  </si>
-  <si>
-    <t>william TAYLOR</t>
-  </si>
-  <si>
-    <t>MARY moore</t>
-  </si>
-  <si>
-    <t>john jackson</t>
-  </si>
-  <si>
-    <t>MICHAEL Anderson</t>
-  </si>
-  <si>
-    <t>ELIZABETH DAVIS</t>
-  </si>
-  <si>
-    <t>ELIZABETH jackson</t>
-  </si>
-  <si>
-    <t>MARY TAYLOR</t>
-  </si>
-  <si>
-    <t>ELIZABETH THOMAS</t>
-  </si>
-  <si>
-    <t>barbara smith</t>
-  </si>
-  <si>
-    <t>robert brown</t>
-  </si>
-  <si>
-    <t>James wilson</t>
-  </si>
-  <si>
-    <t>john wilson</t>
-  </si>
-  <si>
-    <t>william wilson</t>
-  </si>
-  <si>
-    <t>patricia wilson</t>
-  </si>
-  <si>
-    <t>LINDA brown</t>
-  </si>
-  <si>
-    <t>robert moore</t>
-  </si>
-  <si>
-    <t>James smith</t>
-  </si>
-  <si>
-    <t>john moore</t>
-  </si>
-  <si>
-    <t>patricia THOMAS</t>
-  </si>
-  <si>
-    <t>barbara brown</t>
-  </si>
-  <si>
-    <t>LINDA smith</t>
-  </si>
-  <si>
-    <t>john DAVIS</t>
-  </si>
-  <si>
-    <t>john Anderson</t>
-  </si>
-  <si>
-    <t>ELIZABETH TAYLOR</t>
-  </si>
-  <si>
-    <t>william THOMAS</t>
-  </si>
-  <si>
-    <t>MARY smith</t>
-  </si>
-  <si>
-    <t>john brown</t>
-  </si>
-  <si>
-    <t>James DAVIS</t>
-  </si>
-  <si>
-    <t>MARY THOMAS</t>
-  </si>
-  <si>
-    <t>william jackson</t>
-  </si>
-  <si>
     <t>Final Clean</t>
   </si>
   <si>
@@ -1408,21 +1426,6 @@
   </si>
   <si>
     <t>Sheet</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of TotalSales</t>
-  </si>
-  <si>
-    <t>Details for Sum of TotalSales - CleanProduct: Laptop</t>
-  </si>
-  <si>
-    <t>Count of OrderID</t>
   </si>
 </sst>
 </file>
@@ -1430,9 +1433,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1469,7 +1472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1482,16 +1485,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <b/>
@@ -1521,24 +1520,7 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1629,6 +1611,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -1729,6 +1714,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -4385,7 +4373,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{879CBB1C-115B-416D-9BC1-91266EB9854D}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{879CBB1C-115B-416D-9BC1-91266EB9854D}" name="PivotTable3" cacheId="349" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -4474,7 +4462,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D31F00D7-385E-407F-A0B8-13C9B0936E9D}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D31F00D7-385E-407F-A0B8-13C9B0936E9D}" name="PivotTable4" cacheId="349" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField showAll="0"/>
@@ -4587,7 +4575,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAF04773-252D-4046-B8B1-376AE2A6FD45}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAF04773-252D-4046-B8B1-376AE2A6FD45}" name="PivotTable2" cacheId="348" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField showAll="0"/>
@@ -4659,7 +4647,7 @@
     <dataField name="Sum of TotalSales" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="14" count="1">
@@ -4711,7 +4699,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4735AC90-E746-4347-877B-B499FA965682}" name="Table1" displayName="Table1" ref="A1:T99" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4735AC90-E746-4347-877B-B499FA965682}" name="Table1" displayName="Table1" ref="A1:T99" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:T99" xr:uid="{4735AC90-E746-4347-877B-B499FA965682}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{98C972F6-579E-4987-AFF2-6A610047AC32}" name="OrderID"/>
@@ -5025,14 +5013,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5067,7 +5055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -5102,7 +5090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2002</v>
       </c>
@@ -5137,7 +5125,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2003</v>
       </c>
@@ -5172,7 +5160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2004</v>
       </c>
@@ -5207,7 +5195,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>2005</v>
       </c>
@@ -5242,7 +5230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>2006</v>
       </c>
@@ -5277,7 +5265,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>2007</v>
       </c>
@@ -5312,7 +5300,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -5347,7 +5335,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2009</v>
       </c>
@@ -5382,7 +5370,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>2010</v>
       </c>
@@ -5417,7 +5405,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>2011</v>
       </c>
@@ -5452,7 +5440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>2012</v>
       </c>
@@ -5487,7 +5475,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>2013</v>
       </c>
@@ -5522,7 +5510,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>2014</v>
       </c>
@@ -5557,7 +5545,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>2015</v>
       </c>
@@ -5592,7 +5580,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>2016</v>
       </c>
@@ -5627,7 +5615,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>2017</v>
       </c>
@@ -5662,7 +5650,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>2018</v>
       </c>
@@ -5697,7 +5685,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -5732,7 +5720,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -5767,7 +5755,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>2006</v>
       </c>
@@ -5802,7 +5790,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>2022</v>
       </c>
@@ -5837,7 +5825,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>2023</v>
       </c>
@@ -5872,7 +5860,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>2024</v>
       </c>
@@ -5907,7 +5895,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>2025</v>
       </c>
@@ -5942,7 +5930,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>2026</v>
       </c>
@@ -5977,7 +5965,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>2027</v>
       </c>
@@ -6012,7 +6000,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>2028</v>
       </c>
@@ -6047,7 +6035,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>2029</v>
       </c>
@@ -6082,7 +6070,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>2030</v>
       </c>
@@ -6117,7 +6105,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>2031</v>
       </c>
@@ -6152,7 +6140,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>2032</v>
       </c>
@@ -6187,7 +6175,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>2033</v>
       </c>
@@ -6222,7 +6210,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>2034</v>
       </c>
@@ -6257,7 +6245,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>2035</v>
       </c>
@@ -6292,7 +6280,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>2036</v>
       </c>
@@ -6327,7 +6315,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>2037</v>
       </c>
@@ -6362,7 +6350,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>2038</v>
       </c>
@@ -6397,7 +6385,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>2039</v>
       </c>
@@ -6432,7 +6420,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>2040</v>
       </c>
@@ -6467,7 +6455,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>2041</v>
       </c>
@@ -6502,7 +6490,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>2042</v>
       </c>
@@ -6537,7 +6525,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>2043</v>
       </c>
@@ -6572,7 +6560,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>2044</v>
       </c>
@@ -6607,7 +6595,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>2045</v>
       </c>
@@ -6642,7 +6630,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>2011</v>
       </c>
@@ -6677,7 +6665,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>2047</v>
       </c>
@@ -6712,7 +6700,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>2048</v>
       </c>
@@ -6747,7 +6735,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>2049</v>
       </c>
@@ -6782,7 +6770,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>2050</v>
       </c>
@@ -6817,7 +6805,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>2051</v>
       </c>
@@ -6852,7 +6840,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>2052</v>
       </c>
@@ -6887,7 +6875,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>2053</v>
       </c>
@@ -6922,7 +6910,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>2054</v>
       </c>
@@ -6957,7 +6945,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>2055</v>
       </c>
@@ -6992,7 +6980,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>2056</v>
       </c>
@@ -7027,7 +7015,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11">
       <c r="A58">
         <v>2057</v>
       </c>
@@ -7062,7 +7050,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>2058</v>
       </c>
@@ -7097,7 +7085,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>2059</v>
       </c>
@@ -7132,7 +7120,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>2060</v>
       </c>
@@ -7167,7 +7155,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>2061</v>
       </c>
@@ -7202,7 +7190,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>2062</v>
       </c>
@@ -7237,7 +7225,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>2063</v>
       </c>
@@ -7272,7 +7260,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>2064</v>
       </c>
@@ -7307,7 +7295,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>2065</v>
       </c>
@@ -7342,7 +7330,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>2066</v>
       </c>
@@ -7377,7 +7365,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>2067</v>
       </c>
@@ -7412,7 +7400,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="A69">
         <v>2068</v>
       </c>
@@ -7447,7 +7435,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>2069</v>
       </c>
@@ -7482,7 +7470,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>2070</v>
       </c>
@@ -7517,7 +7505,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>2071</v>
       </c>
@@ -7552,7 +7540,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>2072</v>
       </c>
@@ -7587,7 +7575,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>2073</v>
       </c>
@@ -7622,7 +7610,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>2074</v>
       </c>
@@ -7657,7 +7645,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>2075</v>
       </c>
@@ -7692,7 +7680,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="A77">
         <v>2076</v>
       </c>
@@ -7727,7 +7715,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11">
       <c r="A78">
         <v>2077</v>
       </c>
@@ -7762,7 +7750,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11">
       <c r="A79">
         <v>2078</v>
       </c>
@@ -7797,7 +7785,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="A80">
         <v>2079</v>
       </c>
@@ -7832,7 +7820,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11">
       <c r="A81">
         <v>2080</v>
       </c>
@@ -7867,7 +7855,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11">
       <c r="A82">
         <v>2081</v>
       </c>
@@ -7902,7 +7890,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11">
       <c r="A83">
         <v>2082</v>
       </c>
@@ -7937,7 +7925,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11">
       <c r="A84">
         <v>2083</v>
       </c>
@@ -7972,7 +7960,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11">
       <c r="A85">
         <v>2084</v>
       </c>
@@ -8007,7 +7995,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11">
       <c r="A86">
         <v>2085</v>
       </c>
@@ -8042,7 +8030,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11">
       <c r="A87">
         <v>2086</v>
       </c>
@@ -8077,7 +8065,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11">
       <c r="A88">
         <v>2087</v>
       </c>
@@ -8112,7 +8100,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11">
       <c r="A89">
         <v>2088</v>
       </c>
@@ -8147,7 +8135,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11">
       <c r="A90">
         <v>2089</v>
       </c>
@@ -8182,7 +8170,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11">
       <c r="A91">
         <v>2090</v>
       </c>
@@ -8217,7 +8205,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11">
       <c r="A92">
         <v>2091</v>
       </c>
@@ -8252,7 +8240,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11">
       <c r="A93">
         <v>2092</v>
       </c>
@@ -8287,7 +8275,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11">
       <c r="A94">
         <v>2093</v>
       </c>
@@ -8322,7 +8310,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11">
       <c r="A95">
         <v>2094</v>
       </c>
@@ -8357,7 +8345,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11">
       <c r="A96">
         <v>2095</v>
       </c>
@@ -8392,7 +8380,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11">
       <c r="A97">
         <v>2096</v>
       </c>
@@ -8427,7 +8415,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11">
       <c r="A98">
         <v>2097</v>
       </c>
@@ -8462,7 +8450,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11">
       <c r="A99">
         <v>2098</v>
       </c>
@@ -8497,7 +8485,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11">
       <c r="A100">
         <v>2099</v>
       </c>
@@ -8532,7 +8520,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11">
       <c r="A101">
         <v>2100</v>
       </c>
@@ -8575,76 +8563,76 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D5FB16-81D0-4CB2-AB5E-D8D3B149030A}">
   <dimension ref="A3:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>21576</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>24273</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>17980</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>9889</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B8" s="6">
+        <v>228</v>
+      </c>
+      <c r="B8">
         <v>73718</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>22</v>
       </c>
     </row>
@@ -8656,105 +8644,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97F0F1FC-6F54-4E7E-B4C2-14FB787D8124}">
   <dimension ref="A3:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="6">
+        <v>229</v>
+      </c>
+      <c r="B4">
         <v>4495</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B5" s="6">
+        <v>230</v>
+      </c>
+      <c r="B5">
         <v>4495</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B6" s="6">
+        <v>231</v>
+      </c>
+      <c r="B6">
         <v>4495</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B7" s="6">
+        <v>232</v>
+      </c>
+      <c r="B7">
         <v>4495</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B8" s="6">
+        <v>233</v>
+      </c>
+      <c r="B8">
         <v>4495</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="6">
+        <v>234</v>
+      </c>
+      <c r="B9">
         <v>4495</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B10" s="6">
+        <v>235</v>
+      </c>
+      <c r="B10">
         <v>4495</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B11" s="6">
+        <v>236</v>
+      </c>
+      <c r="B11">
         <v>6293</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B12" s="6">
+        <v>237</v>
+      </c>
+      <c r="B12">
         <v>4495</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B13" s="6">
+        <v>238</v>
+      </c>
+      <c r="B13">
         <v>7192</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B14" s="6">
+        <v>228</v>
+      </c>
+      <c r="B14">
         <v>49445</v>
       </c>
     </row>
@@ -8766,36 +8754,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05723860-2EA6-41BA-89FD-A20EFFF55EBC}">
   <dimension ref="A1:T25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -8830,34 +8818,34 @@
         <v>10</v>
       </c>
       <c r="L3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M3" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="N3" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="O3" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="P3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="Q3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="R3" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="S3" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="T3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2093</v>
       </c>
@@ -8895,31 +8883,31 @@
         <v>157</v>
       </c>
       <c r="M4" t="s">
-        <v>423</v>
+        <v>249</v>
       </c>
       <c r="N4" t="s">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="O4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S4" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -8957,31 +8945,31 @@
         <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="N5" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="O5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S5" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>2092</v>
       </c>
@@ -9022,28 +9010,28 @@
         <v>213</v>
       </c>
       <c r="N6" t="s">
-        <v>343</v>
+        <v>235</v>
       </c>
       <c r="O6" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P6" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S6" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T6" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>2004</v>
       </c>
@@ -9081,31 +9069,31 @@
         <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N7" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O7" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P7" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S7" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>2091</v>
       </c>
@@ -9143,31 +9131,31 @@
         <v>211</v>
       </c>
       <c r="M8" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="N8" t="s">
-        <v>342</v>
+        <v>265</v>
       </c>
       <c r="O8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S8" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T8" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>2088</v>
       </c>
@@ -9205,31 +9193,31 @@
         <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>403</v>
+        <v>269</v>
       </c>
       <c r="N9" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="O9" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P9" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S9" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>2087</v>
       </c>
@@ -9270,28 +9258,28 @@
         <v>195</v>
       </c>
       <c r="N10" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="O10" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P10" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S10" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>2086</v>
       </c>
@@ -9329,31 +9317,31 @@
         <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="N11" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="O11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S11" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>2080</v>
       </c>
@@ -9391,31 +9379,31 @@
         <v>197</v>
       </c>
       <c r="M12" t="s">
-        <v>434</v>
+        <v>277</v>
       </c>
       <c r="N12" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="O12" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S12" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>2010</v>
       </c>
@@ -9453,31 +9441,31 @@
         <v>54</v>
       </c>
       <c r="M13" t="s">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="N13" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="O13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S13" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>2011</v>
       </c>
@@ -9515,31 +9503,31 @@
         <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="N14" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="O14" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S14" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T14" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>2012</v>
       </c>
@@ -9577,31 +9565,31 @@
         <v>60</v>
       </c>
       <c r="M15" t="s">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="N15" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="O15" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S15" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>2075</v>
       </c>
@@ -9639,31 +9627,31 @@
         <v>189</v>
       </c>
       <c r="M16" t="s">
-        <v>433</v>
+        <v>283</v>
       </c>
       <c r="N16" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="O16" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P16" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S16" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T16" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>2074</v>
       </c>
@@ -9701,31 +9689,31 @@
         <v>139</v>
       </c>
       <c r="M17" t="s">
-        <v>415</v>
+        <v>286</v>
       </c>
       <c r="N17" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="O17" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P17" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S17" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T17" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18">
         <v>2054</v>
       </c>
@@ -9763,31 +9751,31 @@
         <v>155</v>
       </c>
       <c r="M18" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="N18" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="O18" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P18" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S18" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T18" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>2043</v>
       </c>
@@ -9825,31 +9813,31 @@
         <v>136</v>
       </c>
       <c r="M19" t="s">
-        <v>414</v>
+        <v>291</v>
       </c>
       <c r="N19" t="s">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="O19" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S19" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>2039</v>
       </c>
@@ -9887,31 +9875,31 @@
         <v>129</v>
       </c>
       <c r="M20" t="s">
-        <v>412</v>
+        <v>292</v>
       </c>
       <c r="N20" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="O20" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S20" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T20" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>2033</v>
       </c>
@@ -9949,31 +9937,31 @@
         <v>118</v>
       </c>
       <c r="M21" t="s">
-        <v>408</v>
+        <v>295</v>
       </c>
       <c r="N21" t="s">
-        <v>307</v>
+        <v>233</v>
       </c>
       <c r="O21" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S21" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T21" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>2031</v>
       </c>
@@ -10011,31 +9999,31 @@
         <v>114</v>
       </c>
       <c r="M22" t="s">
-        <v>407</v>
+        <v>296</v>
       </c>
       <c r="N22" t="s">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S22" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T22" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>2030</v>
       </c>
@@ -10073,31 +10061,31 @@
         <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O23" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S23" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>2027</v>
       </c>
@@ -10135,31 +10123,31 @@
         <v>105</v>
       </c>
       <c r="M24" t="s">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="N24" t="s">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="O24" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S24" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T24" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>2024</v>
       </c>
@@ -10200,25 +10188,25 @@
         <v>66</v>
       </c>
       <c r="N25" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O25" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S25" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T25" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -10232,65 +10220,65 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{000F52AC-F326-4C7C-BC25-F631C3BEA12A}">
   <dimension ref="A3:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="6">
+        <v>251</v>
+      </c>
+      <c r="B4">
         <v>73718</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="7">
+        <v>300</v>
+      </c>
+      <c r="B5" s="6">
         <v>36348</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="6">
+        <v>301</v>
+      </c>
+      <c r="B6">
         <v>30938</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="6">
+        <v>302</v>
+      </c>
+      <c r="B7">
         <v>14950</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="6">
+        <v>303</v>
+      </c>
+      <c r="B8">
         <v>6408</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B9" s="6">
+        <v>228</v>
+      </c>
+      <c r="B9">
         <v>162362</v>
       </c>
     </row>
@@ -10302,29 +10290,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DF6152-1FB2-4864-AF84-7C353A4848A3}">
   <dimension ref="A1:T112"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="24.21875" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="13.77734375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
     <col min="16" max="16" width="15" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" customWidth="1"/>
-    <col min="20" max="20" width="11.21875" customWidth="1"/>
+    <col min="19" max="20" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="28.9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10359,34 +10346,34 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -10424,31 +10411,31 @@
         <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="N2" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="O2" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P2" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S2" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>2002</v>
       </c>
@@ -10486,31 +10473,31 @@
         <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="N3" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="O3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S3" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2003</v>
       </c>
@@ -10548,31 +10535,31 @@
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="N4" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="O4" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P4" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S4" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>2004</v>
       </c>
@@ -10610,31 +10597,31 @@
         <v>29</v>
       </c>
       <c r="M5" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N5" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S5" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>2005</v>
       </c>
@@ -10672,31 +10659,31 @@
         <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="N6" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="O6" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P6" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S6" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>2006</v>
       </c>
@@ -10734,31 +10721,31 @@
         <v>38</v>
       </c>
       <c r="M7" t="s">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="N7" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="O7" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S7" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>2007</v>
       </c>
@@ -10796,31 +10783,31 @@
         <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="N8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="O8" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P8" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S8" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T8" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -10858,31 +10845,31 @@
         <v>47</v>
       </c>
       <c r="M9" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="N9" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="O9" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P9" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S9" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>2009</v>
       </c>
@@ -10920,31 +10907,31 @@
         <v>51</v>
       </c>
       <c r="M10" t="s">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="N10" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="O10" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P10" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S10" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>2010</v>
       </c>
@@ -10982,31 +10969,31 @@
         <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="N11" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="O11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S11" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>2011</v>
       </c>
@@ -11044,31 +11031,31 @@
         <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="N12" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="O12" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S12" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T12" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>2012</v>
       </c>
@@ -11106,31 +11093,31 @@
         <v>60</v>
       </c>
       <c r="M13" t="s">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="N13" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="O13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S13" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>2013</v>
       </c>
@@ -11168,31 +11155,31 @@
         <v>63</v>
       </c>
       <c r="M14" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="N14" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="O14" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S14" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T14" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>2014</v>
       </c>
@@ -11233,28 +11220,28 @@
         <v>66</v>
       </c>
       <c r="N15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O15" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P15" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S15" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>2015</v>
       </c>
@@ -11292,31 +11279,31 @@
         <v>71</v>
       </c>
       <c r="M16" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="N16" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="O16" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P16" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S16" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T16" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>2016</v>
       </c>
@@ -11354,31 +11341,31 @@
         <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="N17" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="O17" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S17" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T17" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18">
         <v>2017</v>
       </c>
@@ -11416,31 +11403,31 @@
         <v>81</v>
       </c>
       <c r="M18" t="s">
-        <v>398</v>
+        <v>326</v>
       </c>
       <c r="N18" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="O18" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S18" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>2018</v>
       </c>
@@ -11478,31 +11465,31 @@
         <v>84</v>
       </c>
       <c r="M19" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="N19" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="O19" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P19" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S19" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T19" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -11540,31 +11527,31 @@
         <v>87</v>
       </c>
       <c r="M20" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="N20" t="s">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="O20" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P20" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S20" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T20" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -11602,31 +11589,31 @@
         <v>90</v>
       </c>
       <c r="M21" t="s">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="N21" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="O21" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P21" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S21" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T21" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>2022</v>
       </c>
@@ -11664,31 +11651,31 @@
         <v>93</v>
       </c>
       <c r="M22" t="s">
-        <v>402</v>
+        <v>334</v>
       </c>
       <c r="N22" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="O22" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S22" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T22" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>2023</v>
       </c>
@@ -11726,31 +11713,31 @@
         <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O23" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S23" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>2024</v>
       </c>
@@ -11791,28 +11778,28 @@
         <v>66</v>
       </c>
       <c r="N24" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O24" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S24" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T24" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>2025</v>
       </c>
@@ -11850,31 +11837,31 @@
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>403</v>
+        <v>269</v>
       </c>
       <c r="N25" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="O25" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P25" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S25" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T25" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26">
         <v>2026</v>
       </c>
@@ -11912,31 +11899,31 @@
         <v>11</v>
       </c>
       <c r="M26" t="s">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="N26" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="O26" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
       <c r="R26" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S26" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T26" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27">
         <v>2027</v>
       </c>
@@ -11974,31 +11961,31 @@
         <v>105</v>
       </c>
       <c r="M27" t="s">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
       </c>
       <c r="R27" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S27" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T27" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28">
         <v>2028</v>
       </c>
@@ -12036,31 +12023,31 @@
         <v>108</v>
       </c>
       <c r="M28" t="s">
-        <v>405</v>
+        <v>336</v>
       </c>
       <c r="N28" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S28" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T28" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29">
         <v>2029</v>
       </c>
@@ -12098,31 +12085,31 @@
         <v>111</v>
       </c>
       <c r="M29" t="s">
-        <v>406</v>
+        <v>338</v>
       </c>
       <c r="N29" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S29" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T29" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30">
         <v>2030</v>
       </c>
@@ -12160,31 +12147,31 @@
         <v>29</v>
       </c>
       <c r="M30" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O30" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S30" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T30" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31">
         <v>2031</v>
       </c>
@@ -12222,31 +12209,31 @@
         <v>114</v>
       </c>
       <c r="M31" t="s">
-        <v>407</v>
+        <v>296</v>
       </c>
       <c r="N31" t="s">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="O31" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P31" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S31" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T31" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>2032</v>
       </c>
@@ -12287,28 +12274,28 @@
         <v>116</v>
       </c>
       <c r="N32" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="O32" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P32" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q32" t="b">
         <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S32" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T32" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33">
         <v>2033</v>
       </c>
@@ -12346,31 +12333,31 @@
         <v>118</v>
       </c>
       <c r="M33" t="s">
-        <v>408</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s">
-        <v>307</v>
+        <v>233</v>
       </c>
       <c r="O33" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P33" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S33" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T33" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34">
         <v>2034</v>
       </c>
@@ -12408,31 +12395,31 @@
         <v>120</v>
       </c>
       <c r="M34" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="N34" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="O34" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
       </c>
       <c r="R34" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S34" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T34" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>2035</v>
       </c>
@@ -12470,31 +12457,31 @@
         <v>108</v>
       </c>
       <c r="M35" t="s">
-        <v>405</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s">
+        <v>337</v>
+      </c>
+      <c r="O35" t="s">
         <v>303</v>
       </c>
-      <c r="O35" t="s">
-        <v>264</v>
-      </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
       </c>
       <c r="R35" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S35" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T35" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36">
         <v>2036</v>
       </c>
@@ -12535,28 +12522,28 @@
         <v>123</v>
       </c>
       <c r="N36" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="O36" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P36" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q36" t="b">
         <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S36" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T36" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37">
         <v>2037</v>
       </c>
@@ -12594,31 +12581,31 @@
         <v>125</v>
       </c>
       <c r="M37" t="s">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="N37" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="O37" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P37" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S37" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T37" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38">
         <v>2038</v>
       </c>
@@ -12656,31 +12643,31 @@
         <v>127</v>
       </c>
       <c r="M38" t="s">
-        <v>411</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="O38" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P38" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q38" t="b">
         <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S38" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T38" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39">
         <v>2039</v>
       </c>
@@ -12718,31 +12705,31 @@
         <v>129</v>
       </c>
       <c r="M39" t="s">
-        <v>412</v>
+        <v>292</v>
       </c>
       <c r="N39" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="O39" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P39" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q39" t="b">
         <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S39" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T39" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40">
         <v>2040</v>
       </c>
@@ -12780,31 +12767,31 @@
         <v>84</v>
       </c>
       <c r="M40" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="O40" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q40" t="b">
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S40" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T40" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41">
         <v>2041</v>
       </c>
@@ -12845,28 +12832,28 @@
         <v>132</v>
       </c>
       <c r="N41" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="O41" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q41" t="b">
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S41" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T41" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42">
         <v>2042</v>
       </c>
@@ -12904,31 +12891,31 @@
         <v>134</v>
       </c>
       <c r="M42" t="s">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="O42" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q42" t="b">
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S42" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T42" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43">
         <v>2043</v>
       </c>
@@ -12966,31 +12953,31 @@
         <v>136</v>
       </c>
       <c r="M43" t="s">
-        <v>414</v>
+        <v>291</v>
       </c>
       <c r="N43" t="s">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="O43" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P43" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q43" t="b">
         <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S43" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T43" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44">
         <v>2044</v>
       </c>
@@ -13028,31 +13015,31 @@
         <v>105</v>
       </c>
       <c r="M44" t="s">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="N44" t="s">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="O44" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S44" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T44" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45">
         <v>2045</v>
       </c>
@@ -13090,31 +13077,31 @@
         <v>139</v>
       </c>
       <c r="M45" t="s">
-        <v>415</v>
+        <v>286</v>
       </c>
       <c r="N45" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="O45" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q45" t="b">
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S45" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T45" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46">
         <v>2047</v>
       </c>
@@ -13152,31 +13139,31 @@
         <v>141</v>
       </c>
       <c r="M46" t="s">
-        <v>416</v>
+        <v>351</v>
       </c>
       <c r="N46" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="O46" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q46" t="b">
         <v>1</v>
       </c>
       <c r="R46" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S46" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T46" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47">
         <v>2048</v>
       </c>
@@ -13214,31 +13201,31 @@
         <v>143</v>
       </c>
       <c r="M47" t="s">
-        <v>417</v>
+        <v>353</v>
       </c>
       <c r="N47" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="O47" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q47" t="b">
         <v>1</v>
       </c>
       <c r="R47" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S47" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T47" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48">
         <v>2049</v>
       </c>
@@ -13276,31 +13263,31 @@
         <v>145</v>
       </c>
       <c r="M48" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="N48" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="O48" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q48" t="b">
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S48" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T48" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49">
         <v>2050</v>
       </c>
@@ -13338,31 +13325,31 @@
         <v>118</v>
       </c>
       <c r="M49" t="s">
-        <v>408</v>
+        <v>295</v>
       </c>
       <c r="N49" t="s">
-        <v>307</v>
+        <v>233</v>
       </c>
       <c r="O49" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P49" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q49" t="b">
         <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S49" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T49" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50">
         <v>2051</v>
       </c>
@@ -13400,31 +13387,31 @@
         <v>149</v>
       </c>
       <c r="M50" t="s">
-        <v>419</v>
+        <v>358</v>
       </c>
       <c r="N50" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="O50" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q50" t="b">
         <v>1</v>
       </c>
       <c r="R50" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S50" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T50" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51">
         <v>2052</v>
       </c>
@@ -13462,31 +13449,31 @@
         <v>151</v>
       </c>
       <c r="M51" t="s">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="N51" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="O51" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q51" t="b">
         <v>1</v>
       </c>
       <c r="R51" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S51" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T51" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52">
         <v>2053</v>
       </c>
@@ -13524,31 +13511,31 @@
         <v>153</v>
       </c>
       <c r="M52" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="O52" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q52" t="b">
         <v>1</v>
       </c>
       <c r="R52" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S52" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T52" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53">
         <v>2054</v>
       </c>
@@ -13586,31 +13573,31 @@
         <v>155</v>
       </c>
       <c r="M53" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="N53" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="O53" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q53" t="b">
         <v>1</v>
       </c>
       <c r="R53" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S53" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T53" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54">
         <v>2055</v>
       </c>
@@ -13648,31 +13635,31 @@
         <v>157</v>
       </c>
       <c r="M54" t="s">
-        <v>423</v>
+        <v>249</v>
       </c>
       <c r="N54" t="s">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="O54" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P54" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q54" t="b">
         <v>1</v>
       </c>
       <c r="R54" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S54" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T54" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55">
         <v>2056</v>
       </c>
@@ -13713,28 +13700,28 @@
         <v>159</v>
       </c>
       <c r="N55" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="O55" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q55" t="b">
         <v>1</v>
       </c>
       <c r="R55" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S55" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T55" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56">
         <v>2057</v>
       </c>
@@ -13772,31 +13759,31 @@
         <v>153</v>
       </c>
       <c r="M56" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="N56" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="O56" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q56" t="b">
         <v>1</v>
       </c>
       <c r="R56" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S56" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T56" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57">
         <v>2058</v>
       </c>
@@ -13834,31 +13821,31 @@
         <v>162</v>
       </c>
       <c r="M57" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="N57" t="s">
-        <v>326</v>
+        <v>366</v>
       </c>
       <c r="O57" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q57" t="b">
         <v>1</v>
       </c>
       <c r="R57" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S57" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T57" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58">
         <v>2059</v>
       </c>
@@ -13896,31 +13883,31 @@
         <v>84</v>
       </c>
       <c r="M58" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="N58" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="O58" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q58" t="b">
         <v>1</v>
       </c>
       <c r="R58" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S58" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T58" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59">
         <v>2060</v>
       </c>
@@ -13961,28 +13948,28 @@
         <v>116</v>
       </c>
       <c r="N59" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="O59" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q59" t="b">
         <v>1</v>
       </c>
       <c r="R59" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S59" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T59" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60">
         <v>2061</v>
       </c>
@@ -14023,28 +14010,28 @@
         <v>66</v>
       </c>
       <c r="N60" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O60" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q60" t="b">
         <v>1</v>
       </c>
       <c r="R60" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S60" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T60" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61">
         <v>2062</v>
       </c>
@@ -14082,31 +14069,31 @@
         <v>167</v>
       </c>
       <c r="M61" t="s">
-        <v>425</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="O61" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q61" t="b">
         <v>1</v>
       </c>
       <c r="R61" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S61" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T61" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
       <c r="A62">
         <v>2063</v>
       </c>
@@ -14144,31 +14131,31 @@
         <v>169</v>
       </c>
       <c r="M62" t="s">
-        <v>426</v>
+        <v>369</v>
       </c>
       <c r="N62" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="O62" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q62" t="b">
         <v>1</v>
       </c>
       <c r="R62" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S62" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T62" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
       <c r="A63">
         <v>2064</v>
       </c>
@@ -14206,31 +14193,31 @@
         <v>171</v>
       </c>
       <c r="M63" t="s">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="N63" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="O63" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P63" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q63" t="b">
         <v>1</v>
       </c>
       <c r="R63" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S63" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T63" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
       <c r="A64">
         <v>2065</v>
       </c>
@@ -14268,31 +14255,31 @@
         <v>42</v>
       </c>
       <c r="M64" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="N64" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="O64" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P64" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q64" t="b">
         <v>1</v>
       </c>
       <c r="R64" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S64" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T64" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
       <c r="A65">
         <v>2066</v>
       </c>
@@ -14330,31 +14317,31 @@
         <v>174</v>
       </c>
       <c r="M65" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="N65" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="O65" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P65" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q65" t="b">
         <v>1</v>
       </c>
       <c r="R65" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S65" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T65" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
       <c r="A66">
         <v>2067</v>
       </c>
@@ -14392,31 +14379,31 @@
         <v>71</v>
       </c>
       <c r="M66" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="N66" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="O66" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
       </c>
       <c r="R66" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S66" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T66" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
       <c r="A67">
         <v>2068</v>
       </c>
@@ -14454,31 +14441,31 @@
         <v>177</v>
       </c>
       <c r="M67" t="s">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="N67" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="O67" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q67" t="b">
         <v>1</v>
       </c>
       <c r="R67" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S67" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T67" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
       <c r="A68">
         <v>2069</v>
       </c>
@@ -14516,31 +14503,31 @@
         <v>179</v>
       </c>
       <c r="M68" t="s">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="N68" t="s">
-        <v>332</v>
+        <v>377</v>
       </c>
       <c r="O68" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q68" t="b">
         <v>1</v>
       </c>
       <c r="R68" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S68" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T68" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
       <c r="A69">
         <v>2070</v>
       </c>
@@ -14578,31 +14565,31 @@
         <v>181</v>
       </c>
       <c r="M69" t="s">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="N69" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="O69" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P69" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
       </c>
       <c r="R69" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S69" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T69" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
       <c r="A70">
         <v>2071</v>
       </c>
@@ -14640,31 +14627,31 @@
         <v>171</v>
       </c>
       <c r="M70" t="s">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="N70" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="O70" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P70" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
       </c>
       <c r="R70" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S70" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T70" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
       <c r="A71">
         <v>2072</v>
       </c>
@@ -14702,31 +14689,31 @@
         <v>184</v>
       </c>
       <c r="M71" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="N71" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="O71" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q71" t="b">
         <v>1</v>
       </c>
       <c r="R71" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S71" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T71" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
       <c r="A72">
         <v>2073</v>
       </c>
@@ -14764,31 +14751,31 @@
         <v>186</v>
       </c>
       <c r="M72" t="s">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="N72" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="O72" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
       </c>
       <c r="R72" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S72" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T72" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
       <c r="A73">
         <v>2074</v>
       </c>
@@ -14826,31 +14813,31 @@
         <v>139</v>
       </c>
       <c r="M73" t="s">
-        <v>415</v>
+        <v>286</v>
       </c>
       <c r="N73" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="O73" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
       </c>
       <c r="R73" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S73" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T73" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
       <c r="A74">
         <v>2075</v>
       </c>
@@ -14888,31 +14875,31 @@
         <v>189</v>
       </c>
       <c r="M74" t="s">
-        <v>433</v>
+        <v>283</v>
       </c>
       <c r="N74" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="O74" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
       </c>
       <c r="R74" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S74" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T74" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
       <c r="A75">
         <v>2076</v>
       </c>
@@ -14953,28 +14940,28 @@
         <v>191</v>
       </c>
       <c r="N75" t="s">
-        <v>337</v>
+        <v>384</v>
       </c>
       <c r="O75" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
       </c>
       <c r="R75" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S75" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T75" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
       <c r="A76">
         <v>2077</v>
       </c>
@@ -15012,31 +14999,31 @@
         <v>184</v>
       </c>
       <c r="M76" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="N76" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="O76" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
       </c>
       <c r="R76" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S76" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T76" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
       <c r="A77">
         <v>2078</v>
       </c>
@@ -15074,31 +15061,31 @@
         <v>139</v>
       </c>
       <c r="M77" t="s">
-        <v>415</v>
+        <v>286</v>
       </c>
       <c r="N77" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="O77" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
       </c>
       <c r="R77" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S77" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T77" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
       <c r="A78">
         <v>2079</v>
       </c>
@@ -15139,28 +15126,28 @@
         <v>195</v>
       </c>
       <c r="N78" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="O78" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P78" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
       </c>
       <c r="R78" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S78" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T78" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
       <c r="A79">
         <v>2080</v>
       </c>
@@ -15198,31 +15185,31 @@
         <v>197</v>
       </c>
       <c r="M79" t="s">
-        <v>434</v>
+        <v>277</v>
       </c>
       <c r="N79" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="O79" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q79" t="b">
         <v>1</v>
       </c>
       <c r="R79" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S79" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T79" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
       <c r="A80">
         <v>2081</v>
       </c>
@@ -15260,31 +15247,31 @@
         <v>100</v>
       </c>
       <c r="M80" t="s">
-        <v>403</v>
+        <v>269</v>
       </c>
       <c r="N80" t="s">
+        <v>234</v>
+      </c>
+      <c r="O80" t="s">
         <v>301</v>
       </c>
-      <c r="O80" t="s">
-        <v>262</v>
-      </c>
       <c r="P80" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q80" t="b">
         <v>1</v>
       </c>
       <c r="R80" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S80" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T80" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
       <c r="A81">
         <v>2082</v>
       </c>
@@ -15325,28 +15312,28 @@
         <v>66</v>
       </c>
       <c r="N81" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O81" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q81" t="b">
         <v>1</v>
       </c>
       <c r="R81" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S81" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T81" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
       <c r="A82">
         <v>2083</v>
       </c>
@@ -15384,31 +15371,31 @@
         <v>84</v>
       </c>
       <c r="M82" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="N82" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="O82" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P82" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q82" t="b">
         <v>1</v>
       </c>
       <c r="R82" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S82" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T82" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
       <c r="A83">
         <v>2084</v>
       </c>
@@ -15449,28 +15436,28 @@
         <v>132</v>
       </c>
       <c r="N83" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="O83" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q83" t="b">
         <v>1</v>
       </c>
       <c r="R83" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="S83" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T83" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
       <c r="A84">
         <v>2085</v>
       </c>
@@ -15508,31 +15495,31 @@
         <v>181</v>
       </c>
       <c r="M84" t="s">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="N84" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="O84" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q84" t="b">
         <v>1</v>
       </c>
       <c r="R84" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S84" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T84" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
       <c r="A85">
         <v>2086</v>
       </c>
@@ -15570,31 +15557,31 @@
         <v>60</v>
       </c>
       <c r="M85" t="s">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="N85" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="O85" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q85" t="b">
         <v>1</v>
       </c>
       <c r="R85" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S85" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="T85" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
       <c r="A86">
         <v>2087</v>
       </c>
@@ -15635,28 +15622,28 @@
         <v>195</v>
       </c>
       <c r="N86" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="O86" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q86" t="b">
         <v>1</v>
       </c>
       <c r="R86" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S86" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
       <c r="T86" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
       <c r="A87">
         <v>2088</v>
       </c>
@@ -15694,31 +15681,31 @@
         <v>100</v>
       </c>
       <c r="M87" t="s">
-        <v>403</v>
+        <v>269</v>
       </c>
       <c r="N87" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="O87" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P87" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q87" t="b">
         <v>1</v>
       </c>
       <c r="R87" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S87" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T87" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20">
       <c r="A88">
         <v>2089</v>
       </c>
@@ -15756,31 +15743,31 @@
         <v>207</v>
       </c>
       <c r="M88" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="N88" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="O88" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q88" t="b">
         <v>1</v>
       </c>
       <c r="R88" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S88" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T88" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20">
       <c r="A89">
         <v>2090</v>
       </c>
@@ -15818,31 +15805,31 @@
         <v>209</v>
       </c>
       <c r="M89" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="N89" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="O89" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q89" t="b">
         <v>1</v>
       </c>
       <c r="R89" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S89" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T89" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20">
       <c r="A90">
         <v>2091</v>
       </c>
@@ -15880,31 +15867,31 @@
         <v>211</v>
       </c>
       <c r="M90" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="N90" t="s">
-        <v>342</v>
+        <v>265</v>
       </c>
       <c r="O90" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q90" t="b">
         <v>1</v>
       </c>
       <c r="R90" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="S90" t="s">
-        <v>363</v>
+        <v>267</v>
       </c>
       <c r="T90" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20">
       <c r="A91">
         <v>2092</v>
       </c>
@@ -15945,28 +15932,28 @@
         <v>213</v>
       </c>
       <c r="N91" t="s">
-        <v>343</v>
+        <v>235</v>
       </c>
       <c r="O91" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
       </c>
       <c r="R91" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S91" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="T91" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20">
       <c r="A92">
         <v>2093</v>
       </c>
@@ -16004,31 +15991,31 @@
         <v>157</v>
       </c>
       <c r="M92" t="s">
-        <v>423</v>
+        <v>249</v>
       </c>
       <c r="N92" t="s">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="O92" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Q92" t="b">
         <v>1</v>
       </c>
       <c r="R92" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S92" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T92" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20">
       <c r="A93">
         <v>2094</v>
       </c>
@@ -16066,31 +16053,31 @@
         <v>29</v>
       </c>
       <c r="M93" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="N93" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="O93" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P93" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q93" t="b">
         <v>1</v>
       </c>
       <c r="R93" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S93" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="T93" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20">
       <c r="A94">
         <v>2095</v>
       </c>
@@ -16128,31 +16115,31 @@
         <v>71</v>
       </c>
       <c r="M94" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="N94" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="O94" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q94" t="b">
         <v>1</v>
       </c>
       <c r="R94" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="S94" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T94" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20">
       <c r="A95">
         <v>2096</v>
       </c>
@@ -16190,31 +16177,31 @@
         <v>171</v>
       </c>
       <c r="M95" t="s">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="N95" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="O95" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q95" t="b">
         <v>1</v>
       </c>
       <c r="R95" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="S95" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="T95" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20">
       <c r="A96">
         <v>2097</v>
       </c>
@@ -16252,31 +16239,31 @@
         <v>219</v>
       </c>
       <c r="M96" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="N96" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="O96" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q96" t="b">
         <v>1</v>
       </c>
       <c r="R96" t="s">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="S96" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="T96" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
       <c r="A97">
         <v>2098</v>
       </c>
@@ -16314,31 +16301,31 @@
         <v>221</v>
       </c>
       <c r="M97" t="s">
-        <v>439</v>
+        <v>391</v>
       </c>
       <c r="N97" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="O97" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Q97" t="b">
         <v>1</v>
       </c>
       <c r="R97" t="s">
-        <v>379</v>
+        <v>256</v>
       </c>
       <c r="S97" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="T97" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
       <c r="A98">
         <v>2099</v>
       </c>
@@ -16376,31 +16363,31 @@
         <v>167</v>
       </c>
       <c r="M98" t="s">
-        <v>425</v>
+        <v>367</v>
       </c>
       <c r="N98" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="O98" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="Q98" t="b">
         <v>1</v>
       </c>
       <c r="R98" t="s">
-        <v>377</v>
+        <v>252</v>
       </c>
       <c r="S98" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="T98" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
       <c r="A99">
         <v>2100</v>
       </c>
@@ -16438,85 +16425,85 @@
         <v>71</v>
       </c>
       <c r="M99" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="N99" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="O99" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="Q99" t="b">
         <v>1</v>
       </c>
       <c r="R99" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="S99" t="s">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="T99" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20">
       <c r="A103">
         <f>COUNTA(A2:A101)</f>
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20">
       <c r="A104" t="e" cm="1">
         <f t="array" ref="A104">ROWS(A2:A101)-SUMPRODUCT(1/COUNTIF(A2:A101,A2:A101))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20">
       <c r="A105">
         <f>LEN(B2)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20">
       <c r="A106">
         <f>LEN(TRIM(B2))</f>
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20">
       <c r="A107">
         <f>LEN(B2)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20">
       <c r="A108">
         <f>LEN(L2)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20">
       <c r="A109">
         <f>LEN(B3)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20">
       <c r="A110">
         <f>LEN(M3)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20">
       <c r="A111">
         <f>COUNTIF(Q2:Q101,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20">
       <c r="A112">
         <f>COUNTIF(I2:I99,"&gt;1000")</f>
         <v>56</v>
@@ -16524,7 +16511,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I99">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16538,282 +16525,282 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58F4330-5D12-4FA0-B66F-4FD3E680DCEB}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="34.21875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="43.15">
       <c r="A1" s="3" t="s">
-        <v>234</v>
+        <v>393</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>235</v>
+        <v>394</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>236</v>
+        <v>395</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>397</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>398</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>400</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>401</v>
       </c>
       <c r="F3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>403</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>404</v>
       </c>
       <c r="F4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.9">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>406</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>407</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.9">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>410</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.9">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>250</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>413</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>416</v>
       </c>
       <c r="F8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>418</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>421</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>424</v>
       </c>
       <c r="F11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>427</v>
       </c>
       <c r="F12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
-        <v>277</v>
+        <v>430</v>
       </c>
       <c r="F13" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
+        <v>433</v>
       </c>
       <c r="F14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="C15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.9">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>369</v>
+        <v>437</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="43.15">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>370</v>
+        <v>439</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="C18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="C19" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.9">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
